--- a/feedback_forms/047_superhero_theme_song_feedback--feedback_forms.xlsx
+++ b/feedback_forms/047_superhero_theme_song_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (if other)</t>
+          <t>Superhero Score Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Comments Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Theme Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (if other)</t>
+          <t>Theme Other Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Song Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (if other)</t>
+          <t>Song Other Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1102,29 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>song_title</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Song Title</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>song_liked_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>song_title</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Song Title</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
